--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Bec Chemicals Private Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>levofloxacino hemi-hidratado</t>
+          <t>cetoprofeno</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351957809202431</t>
+          <t>25351184842202351</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,24 +466,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Msn Laboratories Private Limited</t>
+          <t>Ami Lifesciences Private Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>carfilzomibe</t>
+          <t>tadalafila</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25351514099202297</t>
+          <t>25351299954202496</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,24 +493,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shandong Anshun Pharmaceutical Co., Ltd.</t>
+          <t>Kissei Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>piperacilina monoidratada</t>
+          <t>linzagolixato de colina</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25351387641202494</t>
+          <t>25351399700202477</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,24 +520,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Ipca Laboratories Ltd.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cloridrato de lurasidona</t>
+          <t>hidroclorotiazida</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25351221146202413</t>
+          <t>25351227277202595</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,24 +547,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Malladi Drugs &amp; Pharmaceuticals Limited</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cloridrato de pseudoefedrina</t>
+          <t>brexpiprazol</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25351197304202326</t>
+          <t>25351075968202505</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zhuhai Rundu Pharmaceutical Co., Ltd.</t>
+          <t>Heraeus Deutschland Gmbh &amp; Co. Kg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sacubitril valsartana sódica hidratada</t>
+          <t>cloridrato do ácido aminolevulínico</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25351386758202451</t>
+          <t>25351145024202502</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zaklady Farmaceutyczne Polpharma S.A.</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ibandronato de sódio monoidratado</t>
+          <t>dicloridrato de levocetirizina</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25351154041202280</t>
+          <t>25351372678202256</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hubei Biocause Heilen Pharmaceutical Co., Ltd</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dexibuprofeno</t>
+          <t>valsartana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25351138036202491</t>
+          <t>25351508081202337</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hetero Labs Limited</t>
+          <t>Changzhou Pharmaceutical Factory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>enzalutamida</t>
+          <t>lenalidomida</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25351031614202541</t>
+          <t>25351567349202372</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,24 +682,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
+          <t>Ranke Química S.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>linagliptina</t>
+          <t>ebastina</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25351517487202319</t>
+          <t>25351570277202260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,24 +709,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zhejiang Huahai Pharmaceutical Co., Ltd.</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>olmesartana medoxomila</t>
+          <t>gatifloxacino</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25351454271202416</t>
+          <t>25351755793202343</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Honour Lab Limited</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>naproxeno sódico</t>
+          <t>ticagrelor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25351405623202400</t>
+          <t>25351156927202519</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,24 +763,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cloridrato de fingolimode</t>
+          <t>bromidrato de vortioxetina</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25351650003202253</t>
+          <t>25351141871202590</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,142 +790,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lee Pharma Limited</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>flurbiprofeno</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>25351168865202580</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Janssen-Cilag Farmaceutica Ltda</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>cloridrato de icotroquinra</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>25351152307202501</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Novartis Biociencias S.A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>cloridrato de atrasentana</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>25351144061202595</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Orphandc G Importacao E Distribuicao De Produtos Farmaceuticos Ltda</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>pegcetacoplana</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>25351058556202501</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>atorvastatina cálcica tri-hidratada</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>25351420035202498</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>

--- a/novas_cadifas.xlsx
+++ b/novas_cadifas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bec Chemicals Private Limited</t>
+          <t>Zydus Lifesciences Limited</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cetoprofeno</t>
+          <t>bromidrato de vortioxetina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25351184842202351</t>
+          <t>25351141871202590</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,24 +466,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ami Lifesciences Private Limited</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tadalafila</t>
+          <t>levofloxacino hemi-hidratado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25351299954202496</t>
+          <t>25351957809202431</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,24 +493,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kissei Pharmaceutical Co., Ltd.</t>
+          <t>Janssen-Cilag Farmaceutica Ltda</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>linzagolixato de colina</t>
+          <t>cloridrato de icotroquinra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25351399700202477</t>
+          <t>25351152307202501</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,24 +520,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd.</t>
+          <t>Orphandc G Importacao E Distribuicao De Produtos Farmaceuticos Ltda</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hidroclorotiazida</t>
+          <t>pegcetacoplana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25351227277202595</t>
+          <t>25351058556202501</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -547,24 +547,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>brexpiprazol</t>
+          <t>atorvastatina cálcica tri-hidratada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25351075968202505</t>
+          <t>25351420035202498</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,24 +574,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Heraeus Deutschland Gmbh &amp; Co. Kg</t>
+          <t>Laurus Labs Limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cloridrato do ácido aminolevulínico</t>
+          <t>azacitidina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25351145024202502</t>
+          <t>25351293719202249</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Hetero Labs Limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dicloridrato de levocetirizina</t>
+          <t>atorvastatina cálcica tri-hidratada</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25351372678202256</t>
+          <t>25351083726202315</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Anqiu Lu'An Pharmaceutical Co., Ltd.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>valsartana</t>
+          <t>paracetamol</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25351508081202337</t>
+          <t>25351382999202340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,24 +655,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Changzhou Pharmaceutical Factory</t>
+          <t>Micro Labs Limited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lenalidomida</t>
+          <t>cloridrato de lurasidona</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25351567349202372</t>
+          <t>25351155278202440</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,24 +682,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ranke Química S.A.</t>
+          <t>Msn Laboratories Private Limited</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ebastina</t>
+          <t>ciclofosfamida monoidratada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25351570277202260</t>
+          <t>25351705835202303</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,24 +709,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+          <t>Flamma S.P.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gatifloxacino</t>
+          <t>melatonina</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25351755793202343</t>
+          <t>25351449267202347</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Honour Lab Limited</t>
+          <t>Zaklady Farmaceutyczne Polpharma S.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ticagrelor</t>
+          <t>empagliflozina</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25351156927202519</t>
+          <t>25351127180202311</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,24 +763,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Limited</t>
+          <t>Divi'S Laboratories Limited</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bromidrato de vortioxetina</t>
+          <t>carbidopa monoidratada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25351141871202590</t>
+          <t>25351070479202559</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,7 +790,1060 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Limited</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>acetato de abiraterona</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25351364927202311</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aurisco Pharmaceutical Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>acetato de abiraterona</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25351513882202152</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Granules India Limited</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cloridrato de metformina</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25351586381202276</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>paclitaxel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>25351348787202252</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Astellas Farma Brasil Importação E Distribuição De Medicamentos Ltda.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avacincaptade pegol sódico</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25351046702202547</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lee Pharma Limited</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bilastina</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25351035922202383</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>oxalato de escitalopram</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>25351501193202367</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alembic Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>macitentana</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25351000069202541</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Msn Laboratories Private Limited</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cloridrato de olopatadina</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25351456102202241</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Zhejiang Xianju Pharmaceutical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prednisolona</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25351399589202257</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lupin Manufacturing Solutions Limited</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>empagliflozina</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>25351208397202411</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06/08/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Rolabo Outsourcing, S.L.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cloridrato de palonosetrona</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25351860688202325</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>03/12/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dr Reddys Farmacêutica Do Brasil Ltda</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fumarato de dimetila</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25351855399202312</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17/10/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Noramco, Llc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cloridrato de oxicodona</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25351417941202243</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>08/10/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hetero Labs Limited</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>levetiracetam</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25351229934202377</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/07/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Zhejiang Guobang Pharmaceutical Co., Ltd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ciprofloxacino</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>25351097818202200</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>03/05/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Zhejiang Guobang Pharmaceutical Co., Ltd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>claritromicina</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25351082643202228</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/04/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Msn Life Sciences Private Limited</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>bilastina</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>25351010782202331</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Zhejiang Supor Pharmaceuticals Co., Ltd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>hemifumarato de quetiapina</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>25351127200202273</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21/03/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Newchem S.P.A.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>dienogeste</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>25351497379202312</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>002.1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>15/03/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chirogate International Inc.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>bimatoprosta</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>25351403161202216</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/03/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Msn Organics Private Limited</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cloridrato de cinacalcete</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>25351153141202299</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20/02/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cohance Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>hemifumarato de quetiapina</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>25351285445202214</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20/02/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Euroapi Hungary Ltd.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>latanoprosta</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>25351147798202306</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05/12/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aspen Oss B.V.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>budesonida</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>25351036030202219</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24/11/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nortec Química S.A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>micofenolato de sódio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>25351448083202289</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>03/11/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zhuhai United Laboratories Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ampicilina sódica</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>25351433410202117</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>002.1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chemwerth, Inc.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>milrinona</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>25351869642202118</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Intas Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>carfilzomibe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>25351255810202185</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/08/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Centrient Pharmaceuticals Spain, S.A.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cefalexina monoidratada</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>25351196266202122</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17/08/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chemo Do Brasil Comércio De Farmoquímicos Ltda</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>drospirenona</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>25351273206202211</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/05/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shandong Anshun Pharmaceutical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tazobactam</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>25351088152202291</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>09/05/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Shandong Anshun Pharmaceutical Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>piperacilina monoidratada</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>25351088151202246</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>30/03/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Fersinsa Gb S.A. De C.V.</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>benzilpenicilina potássica</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>25351881526202169</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/02/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Alembic Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>succinato de desvenlafaxina monoidratado</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>25351114763202111</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07/12/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Synthimed Labs Private Limited</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>claritromicina</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>25351517246202281</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18/10/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shilpa Pharma Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cloridrato de bendamustina monoidratada</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>25351748374202193</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>14/10/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fersinsa Gb S.A. De C.V.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>amoxicilina tri-hidratada</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>25351533263202001</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>08/08/2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Viyash Scientific Limited</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cloridrato  de ondansetrona di-hidratado</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>25351163773202180</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>001.1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>23/02/2022</t>
         </is>
       </c>
     </row>
